--- a/testdata/excel/recruitment_data.xlsx
+++ b/testdata/excel/recruitment_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="60">
   <si>
     <t>scenario</t>
   </si>
@@ -37,6 +37,36 @@
     <t>resume_name</t>
   </si>
   <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>google_drive_link</t>
+  </si>
+  <si>
+    <t>candidate_name</t>
+  </si>
+  <si>
+    <t>start_date</t>
+  </si>
+  <si>
+    <t>end_date</t>
+  </si>
+  <si>
+    <t>interviewer_name</t>
+  </si>
+  <si>
+    <t>from_date</t>
+  </si>
+  <si>
+    <t>to_date</t>
+  </si>
+  <si>
+    <t>interviewer_mail</t>
+  </si>
+  <si>
+    <t>slot_duration</t>
+  </si>
+  <si>
     <t>Upload document and verify its status</t>
   </si>
   <si>
@@ -85,6 +115,9 @@
     <t>Upload resume with unsupported file format</t>
   </si>
   <si>
+    <t>String Methods Programs.txt</t>
+  </si>
+  <si>
     <t>Some files were skipped. Only PDF and DOCX files are supported.</t>
   </si>
   <si>
@@ -103,7 +136,64 @@
     <t>QA Engineer</t>
   </si>
   <si>
-    <t>String Methods Programs.txt</t>
+    <t>Connect Google Drive and Verify Candidate Profile</t>
+  </si>
+  <si>
+    <t>Test Engineer (Software Testing)</t>
+  </si>
+  <si>
+    <t>Google Drive Folder</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1McKz4CeA8k6TcQnjtseBzJ15Sk1k0hSE?usp=sharing</t>
+  </si>
+  <si>
+    <t>Add interview slot manually and verify date and time</t>
+  </si>
+  <si>
+    <t>May 8, 2026 08:00 AM</t>
+  </si>
+  <si>
+    <t>May 8, 2026 09:00 AM</t>
+  </si>
+  <si>
+    <t>John Doe</t>
+  </si>
+  <si>
+    <t>Sync interview slot from calendar and verify date and time</t>
+  </si>
+  <si>
+    <t>harikrishnamunjala@yanthraa.com</t>
+  </si>
+  <si>
+    <t>30 minutes</t>
+  </si>
+  <si>
+    <t>send interview invitation</t>
+  </si>
+  <si>
+    <t>PINJARI SHAMEENA</t>
+  </si>
+  <si>
+    <t>Re-schedule interview slot and verify status</t>
+  </si>
+  <si>
+    <t>Reschedule</t>
+  </si>
+  <si>
+    <t>Test Interviewer</t>
+  </si>
+  <si>
+    <t>Cancel scheduled interview and verify status</t>
+  </si>
+  <si>
+    <t>CANCELLED</t>
+  </si>
+  <si>
+    <t>Submit feedback and verify</t>
+  </si>
+  <si>
+    <t>HIRE</t>
   </si>
 </sst>
 </file>
@@ -435,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="72.36328125" bestFit="1" customWidth="1"/>
@@ -443,11 +533,14 @@
     <col min="3" max="3" width="35.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="58.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.90625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="78.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -469,129 +562,285 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="F11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
         <v>28</v>
+      </c>
+      <c r="F12" t="s">
+        <v>39</v>
+      </c>
+      <c r="N12" t="s">
+        <v>45</v>
+      </c>
+      <c r="O12" t="s">
+        <v>46</v>
+      </c>
+      <c r="P12" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" t="s">
+        <v>39</v>
+      </c>
+      <c r="K14" t="s">
+        <v>45</v>
+      </c>
+      <c r="L14" t="s">
+        <v>46</v>
+      </c>
+      <c r="M14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>